--- a/Result/checksun_type/人造纖維.xlsx
+++ b/Result/checksun_type/人造纖維.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>15.97</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>18.9</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>15379.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>13594.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>13594</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>25949.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>91243.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>91243</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-6419.247633283376</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>15379</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>15379.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>15.89</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>17.36</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>19.0</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>19</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>13780.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>14915.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>14915.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>28391.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>94722.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>94722.53999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-6675.130581576926</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>13780</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>13780.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>15.91</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>17.49</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>19.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>10309.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>21381.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>21381.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>34572.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>97429.82</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>97429.82000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-6630.958701225685</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>10309</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>10309.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>16.11</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>17.65</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>19.2</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>17967.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>25636.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>25636.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>37487.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>103974.56</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>103974.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-5959.143204251566</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>17967</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>17967.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>16.43</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>17.82</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>19.32</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>19.32</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>10535.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>30790.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>30790.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>38710.2</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>113929.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>113929.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-5607.080236993839</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>10535</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>10535.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>16.73</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>19.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>21988.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>38305.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>38305.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>39203.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>121063.92</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>121063.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-4107.594561018734</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>21988</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>21988.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>17.06</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>18.14</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>19.46</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>46109.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>41867.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>41867.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>39269.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>124974.72</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>124974.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-3045.879503875054</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>46109</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>46109.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>17.36</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>18.31</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>19.48</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>31584.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>47763.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>47763.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>37117.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>124558.22</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>124558.22</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-4004.755154245693</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>31584</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>31584.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>17.75</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>18.43</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>19.49</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>43738.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>49339.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>49339.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>35601.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>124438.32</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>124438.32</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-3675.30054212355</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>43738</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>43738.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>17.91</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>18.53</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>48108.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>46629.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>46629.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>33321.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>124688.06</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>124688.06</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-4375.604648301785</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>48108</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>48108.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>18.04</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>19.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>39799.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>40101.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>40101</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>33025.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>125891.7</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>125891.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-5687.981776831337</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>39799</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>39799.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>64.86</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>69.78</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>71.51</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.51000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>133844.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>113436.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>113436.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>143344.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-33996.22435277211</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>133844</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>133844.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>64.94</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>70.04</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>71.67</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.67</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>69938.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>115762.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>115762</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>185899.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-36925.82719326479</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>69938</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>69938.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>65.82000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>70.4</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>71.92</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>71.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>103142.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>132141.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>132141.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>226176.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-32945.12313706632</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>103142</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>103142.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>67.08000000000001</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>70.78</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>72.18</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>70.78</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>72.18000000000001</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>157169.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>132857.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>132857.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>277839.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-29639.36294474467</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>157169</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>157169.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>68.55999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>71.25</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>72.52</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.52</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>103088.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>159804.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>159804.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>276799.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-29646.90685054433</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>103088</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>103088.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>69.46000000000001</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>71.6</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>72.83</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.83</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>145473.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>173253.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>173253</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>283798.0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-22804.47289988157</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>145473</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>145473.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>70.5</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>71.94</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>73.02</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>71.94</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>73.02</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>151835.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>256037.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>256037.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>309369.1</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-16756.37179536757</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>151835</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>151835.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>71.46</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>72.19</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>73.03</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>72.19</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>73.03</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>106722.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>320211.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>320211.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>303245.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>0</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-8199.428367655899</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>106722</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>106722.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>72.25999999999999</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>72.34</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>72.93</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>72.93000000000001</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>291903.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>422820.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>422820.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>301730.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>0</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>9151.14897077711</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>291903</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>291903.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>72.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>72.5</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>72.84</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>72.84</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>170332.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>393795.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>393795</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>296741.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>13770.03984815365</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>170332</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>170332.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>73.19999999999999</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>72.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>72.78</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>72.78</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>559394.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>394343.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>394343</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>295140.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>0</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>32902.13253554323</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>559394</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>559394.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>15.52</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>14.65</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>14.25</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>14.25</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>119624206.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>107589319.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>107589319.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>172922305.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>94607239.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>94607239.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-2022682.634577855</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>119624206</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>119624206.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>14.56</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>14.22</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>64513731.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>117131565.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>117131565.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>189236741.5</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>95136976.66</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>95136976.66</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-811428.0970462263</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>64513731</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>64513731.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>15.62</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>98239880.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>145077701.8</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>145077701.8</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>197710495.1</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>95685238.18</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>95685238.18000001</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>6852608.852893442</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>98239880</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>98239880.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>15.7</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>14.43</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>14.18</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>14.18</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>136757323.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>198870693.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>198870693</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>191072986.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>95826631.28</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>95826631.28</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>13942981.07234681</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>136757323</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>136757323.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>15.71</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>14.17</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>14.17</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>118811458.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>218890197.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>218890197.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>180440528.1</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>94590340.24</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>94590340.23999999</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>19447251.74041066</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>118811458</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>118811458.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>15.62</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>14.14</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>167335434.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>238255292.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>238255292.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>174611066.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>94149821.56</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>94149821.56</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>28538722.09691575</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>167335434</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>167335434.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>14.12</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>14.12</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>14.12</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>204244414.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>261341917.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>261341917.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>164705302.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>93528944.36</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>93528944.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>35308299.38846174</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>204244414</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>204244414.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>15.14</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>13.99</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.1</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>367204836.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>250343288.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>250343288.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>147374313.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>92034279.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>92034279.18000001</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>39763579.82679668</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>367204836</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>367204836.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>14.76</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>13.86</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>14.07</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>14.07</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>236854847.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>183275280.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>183275280.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>113618632.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>88594248.36</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>88594248.36</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>27248093.10203247</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>236854847</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>236854847.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>14.42</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>13.76</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>13.76</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>14.06</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>215636930.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>141990858.4</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>141990858.4</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>94691504.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>86944762.74</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>86944762.73999999</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>22361750.42015383</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>215636930</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>215636930.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>14.12</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>13.66</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>14.05</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>282768562.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>110966841.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>110966841.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>82450380.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>89916501.8</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>89916501.8</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>16855975.18103603</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>282768562</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>282768562.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>31.88</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>30</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>398780549.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>593348955.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>593348955.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1182774146.3</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>558033656.5</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>558033656.5</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-61585052.20607018</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>398780549</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>398780549.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>31.9</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>31.03</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>29.94</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>29.94</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>573811576.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>639140958.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>639140958</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1298204859.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>556181619.44</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>556181619.4400001</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-29185675.31124961</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>573811576</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>573811576.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>32.31</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>31.01</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>29.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>29.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>617869280.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>713943389.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>713943389.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1385381878.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>548956919.2</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>548956919.2</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-611829.9503898621</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>617869280</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>617869280.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>32.72</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>29.84</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>601484505.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>790120467.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>790120467.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1381540589.5</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>540487513.94</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>540487513.9400001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>35509331.92049515</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>601484505</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>601484505.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>33.14</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>30.9</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>29.77</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>29.77</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>774798868.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>1224630852.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>1224630852.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1381352592.0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>530923291.02</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>530923291.02</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>87598312.91745603</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>774798868</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>774798868.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>33.64</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>29.68</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>29.68</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>627740561.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1772199337.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1772199337</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1333371150.1</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>519334570.38</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>519334570.38</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>140313235.7017767</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>627740561</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>627740561.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>33.78</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>29.63</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>29.63</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>947823733.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1957268760.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1957268760.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1319896902.0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>510864125.42</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>510864125.42</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>226365328.4400284</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>947823733</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>947823733.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>33.34</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>30.49</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>29.54</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>29.54</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>998754669.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>2056820368.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>2056820368.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1250860855.8</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>499842523.62</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>499842523.62</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>306917787.9075298</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>998754669</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>998754669.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>32.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>30.29</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>29.45</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2774036430.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1972960711.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1972960711.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>1174625268.3</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>494079808.74</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>494079808.74</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>405574494.4358344</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2774036430</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2774036430.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>31.42</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>30.04</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>29.38</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>29.38</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3512641292.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1538074331.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1538074331.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>941548438.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>446722181.38</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>446722181.38</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>341819083.1392757</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3512641292</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3512641292.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>29.98</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>29.26</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>29.26</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1553087678.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>894542963.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>894542963.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>612270209.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>385550752.82</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>385550752.82</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>159395864.5320747</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1553087678</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1553087678.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>53.48</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>48.7</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>43.68</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>43.68</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>3512622548.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>6095469315.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>6095469315</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>9544851503.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>3663541757.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>3663541757.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>98808707.88450241</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>3512622548</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>3512622548.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>54.02</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>48.25</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>43.41</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>43.41</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>6744255965.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>6936487304.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>6936487304.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>10032139013.4</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>3632131847.42</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>3632131847.42</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>468208784.7071676</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>6744255965</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>6744255965.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>55.0</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>47.74</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>43.12</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>43.12</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>4850127005.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>8366597065.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>8366597065.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>9915210649.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>3525171118.12</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>3525171118.12</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>632955000.321434</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>4850127005</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>4850127005.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>55.34</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>47.15</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>47.15</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>42.8</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>4661687858.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>9917900867.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>9917900867.799999</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>9646311981.3</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>3483979320.62</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>3483979320.62</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>1048643589.758906</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>4661687858</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>4661687858.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>55.96</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>46.69</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>42.52</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>10708653199.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>11555043688.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>11555043688.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>9440522375.4</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>3413291777.02</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>3413291777.02</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>1625222783.642477</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>10708653199</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>10708653199.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>55.4</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>45.98</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>42.16</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>7717712495.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>12994233691.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>12994233691.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>8470087592.9</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>3233128694.92</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>3233128694.92</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>1742974531.810349</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>7717712495</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>7717712495.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>54.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>45.39</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>41.86</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>41.86</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>13894804772.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>13127790722.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>13127790722.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>7823899971.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>3109382048.22</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>3109382048.22</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>2169400157.056937</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>13894804772</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>13894804772.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>52.2</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>44.62</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>41.5</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>41.5</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>12606646015.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>11463824233.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>11463824233.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>6558502593.2</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>2879764455.78</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>2879764455.78</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>2039269729.264316</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>12606646015</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>12606646015.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>43.9</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>41.17</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>41.17</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>12847401961.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>9374723094.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>9374723094.799999</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>5390815186.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>2722439698.1</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>2722439698.1</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>1918555066.051131</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>12847401961</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>12847401961.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>46.94</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>43.19</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>43.19</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>40.9</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>17904603214.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>7326001062.4</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>7326001062.4</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>4299803431.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>2525457286.94</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>2525457286.94</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>1651790443.45904</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>17904603214</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>17904603214.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>44.51000000000001</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>40.69</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>8385497650.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>3945941494.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>3945941494.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>2599113437.9</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>2229827006.08</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>2229827006.08</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>669862618.2396603</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>8385497650</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>8385497650.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>40.04</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>39.79</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>38.9</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>39.79</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>38.9</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>504202980.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>843671193.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>843671193.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1432628587.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>817449144.5</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>817449144.5</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-66364592.2718823</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>504202980</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>504202980.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>40.15</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>39.77</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>38.86</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>38.86</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>1191410722.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1001140841.0</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1001140841</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1612190852.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>817981984.0</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>817981984</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-14108799.98412943</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>1191410722</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>1191410722.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>40.67</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>39.81</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>38.84</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>39.81</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>38.84</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>757743633.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1081544530.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1081544530.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1662546115.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>801871651.48</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>801871651.48</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-12583183.35933495</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>757743633</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>757743633.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>41.19</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>39.78</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>38.8</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>38.8</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>827539453.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1292858575.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1292858575.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1651121749.4</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>795921301.56</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>795921301.5599999</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>36509999.33177662</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>827539453</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>827539453.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>41.7</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>39.8</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>38.76</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>38.76</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>937459181.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>1458881861.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>1458881861.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1666154267.0</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>785879279.18</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>785879279.1799999</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>97861065.3429439</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>937459181</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>937459181.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>41.97000000000001</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>39.68</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>38.69</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>39.68</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>38.69</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1291551216.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>2021585981.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>2021585981</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1636934660.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>778694570.54</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>778694570.54</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>170233293.5966489</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1291551216</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1291551216.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>42.23</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>38.65</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>1593429169.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>2223240863.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>2223240863.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1628447057.6</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>760096745.28</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>760096745.28</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>229603998.2949185</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>1593429169</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>1593429169.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>41.91</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>39.47</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>38.58</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>38.58</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>1814313857.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>2243547701.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>2243547701.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1527257594.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>737882950.9</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>737882950.9</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>273875081.531914</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1814313857</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1814313857.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>41.09</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>39.26</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>38.48</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>39.26</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>38.48</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>1657655883.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2009384923.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2009384923.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1400414235.0</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>713699684.46</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>713699684.46</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>303672016.6729105</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>1657655883</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>1657655883.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>40.3</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>39.0</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>38.4</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>38.4</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3750979780.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>1873426672.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>1873426672.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>1308948214.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>694282279.54</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>694282279.54</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>352178420.6360159</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3750979780</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3750979780.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>39.23999999999999</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>38.72</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>38.33</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>38.33</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>2299825630.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>1252283340.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>1252283340.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>976594682.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>634083400.12</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>634083400.12</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>184610779.4534516</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>2299825630</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>2299825630.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
